--- a/output/MDM_HQ/MDM_HQ_TestReport.xlsx
+++ b/output/MDM_HQ/MDM_HQ_TestReport.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="91">
   <si>
     <t>Profile</t>
   </si>
@@ -47,7 +47,7 @@
     <t>Finished</t>
   </si>
   <si>
-    <t>2026-10-21T13:06:00Z</t>
+    <t>2026-10-21T13:31:00Z</t>
   </si>
   <si>
     <t>Tiles tested</t>
@@ -113,16 +113,19 @@
     <t>WEBGUI</t>
   </si>
   <si>
-    <t>FAIL – Open BP -&gt; B001 (display) (No authorization to display accounts from account group 0120)</t>
-  </si>
-  <si>
-    <t>BP B001 is also a customer (KNA1-KTOKD 0120). Role has F_KNA1_GRP ACTVT = F4 only (SU24 default), no 03/01/02.</t>
-  </si>
-  <si>
-    <t>screens/T01_BP_auth_error.png</t>
-  </si>
-  <si>
-    <t>Maintain F_KNA1_GRP (and F_LFA1_GRP, same pattern) in Z_VOT_BEMIND_MDM_HQ_ALL with ACTVT 01,02,03,06 (FULL per matrix), KTOKD/KTOKK *; regenerate + generate derived roles.</t>
+    <t xml:space="preserve">FAIL – Run 1 (12:50): Open BP -&gt; B001 (display) (No authorization to display accounts from account group 0120 (F_KNA1_GRP ACTVT F4 only))
+PASS – Retest (13:30) after fix: Open BP -&gt; B001 (Display Organization : B001)
+PASS – Relationships (0 relationship(s) found)
+PASS – Exit</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>screens/T01_BP_auth_error.png (before), screens/T01_BP_retest_OK.png (after)</t>
+  </si>
+  <si>
+    <t>FIXED 13:22: F_KNA1_GRP + F_LFA1_GRP ACTVT 01/02/03/06, KTOKD/KTOKK * in _ALL, derived regenerated. Now an automatic rule (config authOverrides).</t>
   </si>
   <si>
     <t>Articles &amp; Purchasing Info Records</t>
@@ -135,9 +138,6 @@
   </si>
   <si>
     <t>MM41</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>Maintain Article</t>
@@ -316,7 +316,7 @@
       <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -331,11 +331,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -366,7 +361,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -382,9 +377,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -794,7 +786,7 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -802,7 +794,7 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -897,8 +889,8 @@
       <c r="H2" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="I2" s="7" t="s">
-        <v>14</v>
+      <c r="I2" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>34</v>
@@ -933,19 +925,19 @@
         <v>13</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>13</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -956,10 +948,10 @@
         <v>38</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>42</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>43</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>32</v>
@@ -971,19 +963,19 @@
         <v>13</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>13</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -994,10 +986,10 @@
         <v>38</v>
       </c>
       <c r="C5" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>45</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>32</v>
@@ -1009,19 +1001,19 @@
         <v>13</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>13</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1029,13 +1021,13 @@
         <v>37</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>49</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>32</v>
@@ -1047,19 +1039,19 @@
         <v>13</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>13</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1067,13 +1059,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>50</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>51</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>32</v>
@@ -1085,19 +1077,19 @@
         <v>13</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>13</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1105,13 +1097,13 @@
         <v>37</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C8" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>52</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>53</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>32</v>
@@ -1123,19 +1115,19 @@
         <v>13</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>13</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1143,51 +1135,51 @@
         <v>37</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="E9" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="F9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H9" s="5" t="s">
+      <c r="I9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="K9" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="I9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>60</v>
-      </c>
       <c r="L9" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C10" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>32</v>
@@ -1199,33 +1191,33 @@
         <v>13</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I10" s="6" t="s">
         <v>13</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C11" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>64</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>65</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>32</v>
@@ -1237,71 +1229,71 @@
         <v>13</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I11" s="6" t="s">
         <v>13</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C12" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="E12" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H12" s="5" t="s">
+      <c r="I12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="K12" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="I12" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="K12" s="5" t="s">
-        <v>69</v>
-      </c>
       <c r="L12" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B13" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="D13" s="5" t="s">
         <v>71</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>72</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>32</v>
@@ -1313,33 +1305,33 @@
         <v>13</v>
       </c>
       <c r="H13" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="K13" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="I13" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="K13" s="5" t="s">
-        <v>74</v>
-      </c>
       <c r="L13" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C14" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>75</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>76</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>32</v>
@@ -1351,36 +1343,36 @@
         <v>13</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I14" s="6" t="s">
         <v>13</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C15" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>78</v>
-      </c>
       <c r="E15" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>13</v>
@@ -1389,71 +1381,71 @@
         <v>13</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C16" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="E16" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H16" s="5" t="s">
+      <c r="I16" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="K16" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="I16" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="K16" s="5" t="s">
+      <c r="L16" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="L16" s="5" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C17" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>86</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>32</v>
@@ -1465,33 +1457,33 @@
         <v>13</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I17" s="6" t="s">
         <v>13</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C18" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>87</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>88</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>32</v>
@@ -1503,33 +1495,33 @@
         <v>13</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I18" s="6" t="s">
         <v>13</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="L18" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C19" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D19" s="5" t="s">
         <v>90</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>91</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>32</v>
@@ -1541,19 +1533,19 @@
         <v>13</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I19" s="6" t="s">
         <v>13</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
